--- a/outputs/step_disease_logistic/auc_delta_summary.xlsx
+++ b/outputs/step_disease_logistic/auc_delta_summary.xlsx
@@ -513,55 +513,55 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0.8083</v>
+        <v>0.7945</v>
       </c>
       <c r="D2">
-        <v>0.8129999999999999</v>
+        <v>0.7965</v>
       </c>
       <c r="E2">
-        <v>0.8179999999999999</v>
+        <v>0.8024</v>
       </c>
       <c r="F2">
-        <v>0.8176</v>
+        <v>0.8106</v>
       </c>
       <c r="G2">
-        <v>0.8198</v>
+        <v>0.8103</v>
       </c>
       <c r="H2">
-        <v>0.0047</v>
+        <v>0.0019</v>
       </c>
       <c r="I2">
-        <v>1.6245</v>
+        <v>0.7488</v>
       </c>
       <c r="J2">
-        <v>0.1043</v>
+        <v>0.454</v>
       </c>
       <c r="K2">
-        <v>0.0051</v>
+        <v>0.0059</v>
       </c>
       <c r="L2">
-        <v>1.1622</v>
+        <v>1.4184</v>
       </c>
       <c r="M2">
-        <v>0.2452</v>
+        <v>0.1561</v>
       </c>
       <c r="N2">
-        <v>0.009299999999999999</v>
+        <v>0.0161</v>
       </c>
       <c r="O2">
-        <v>1.8988</v>
+        <v>2.7775</v>
       </c>
       <c r="P2">
-        <v>0.0576</v>
+        <v>0.0055</v>
       </c>
       <c r="Q2">
-        <v>0.0022</v>
+        <v>-0.0003</v>
       </c>
       <c r="R2">
-        <v>0.618</v>
+        <v>-0.1106</v>
       </c>
       <c r="S2">
-        <v>0.5366</v>
+        <v>0.9119</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -572,55 +572,55 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>0.7144</v>
+        <v>0.7177</v>
       </c>
       <c r="D3">
-        <v>0.7185</v>
+        <v>0.7184</v>
       </c>
       <c r="E3">
-        <v>0.7308</v>
+        <v>0.7296</v>
       </c>
       <c r="F3">
-        <v>0.7285</v>
+        <v>0.7299</v>
       </c>
       <c r="G3">
-        <v>0.7335</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="H3">
-        <v>0.0041</v>
+        <v>0.0007</v>
       </c>
       <c r="I3">
-        <v>1.2583</v>
+        <v>0.2087</v>
       </c>
       <c r="J3">
-        <v>0.2083</v>
+        <v>0.8347</v>
       </c>
       <c r="K3">
+        <v>0.0113</v>
+      </c>
+      <c r="L3">
+        <v>2.334</v>
+      </c>
+      <c r="M3">
+        <v>0.0196</v>
+      </c>
+      <c r="N3">
         <v>0.0123</v>
       </c>
-      <c r="L3">
-        <v>2.5441</v>
-      </c>
-      <c r="M3">
-        <v>0.011</v>
-      </c>
-      <c r="N3">
-        <v>0.0141</v>
-      </c>
       <c r="O3">
-        <v>2.3602</v>
+        <v>1.7142</v>
       </c>
       <c r="P3">
-        <v>0.0183</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.0051</v>
+        <v>0.0035</v>
       </c>
       <c r="R3">
-        <v>1.3016</v>
+        <v>1.1247</v>
       </c>
       <c r="S3">
-        <v>0.1931</v>
+        <v>0.2607</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -631,55 +631,55 @@
         <v>22</v>
       </c>
       <c r="C4">
-        <v>0.7269</v>
+        <v>0.7217</v>
       </c>
       <c r="D4">
-        <v>0.7264</v>
+        <v>0.7206</v>
       </c>
       <c r="E4">
-        <v>0.7482</v>
+        <v>0.7405</v>
       </c>
       <c r="F4">
-        <v>0.7314000000000001</v>
+        <v>0.7231</v>
       </c>
       <c r="G4">
-        <v>0.7458</v>
+        <v>0.7348</v>
       </c>
       <c r="H4">
-        <v>-0.0005</v>
+        <v>-0.001</v>
       </c>
       <c r="I4">
-        <v>-0.1858</v>
+        <v>-1.7907</v>
       </c>
       <c r="J4">
-        <v>0.8526</v>
+        <v>0.0733</v>
       </c>
       <c r="K4">
-        <v>0.0218</v>
+        <v>0.0199</v>
       </c>
       <c r="L4">
-        <v>2.4983</v>
+        <v>2.5246</v>
       </c>
       <c r="M4">
-        <v>0.0125</v>
+        <v>0.0116</v>
       </c>
       <c r="N4">
-        <v>0.0045</v>
+        <v>0.0014</v>
       </c>
       <c r="O4">
-        <v>0.7159</v>
+        <v>0.2281</v>
       </c>
       <c r="P4">
-        <v>0.474</v>
+        <v>0.8196</v>
       </c>
       <c r="Q4">
-        <v>0.0144</v>
+        <v>0.0117</v>
       </c>
       <c r="R4">
-        <v>1.9741</v>
+        <v>1.9599</v>
       </c>
       <c r="S4">
-        <v>0.0484</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -690,55 +690,55 @@
         <v>23</v>
       </c>
       <c r="C5">
-        <v>0.6619</v>
+        <v>0.6655</v>
       </c>
       <c r="D5">
-        <v>0.6627999999999999</v>
+        <v>0.6654</v>
       </c>
       <c r="E5">
-        <v>0.6986</v>
+        <v>0.6811</v>
       </c>
       <c r="F5">
-        <v>0.6742</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="G5">
-        <v>0.6986</v>
+        <v>0.6856</v>
       </c>
       <c r="H5">
-        <v>0.0009</v>
+        <v>-0</v>
       </c>
       <c r="I5">
-        <v>0.3723</v>
+        <v>-0.0589</v>
       </c>
       <c r="J5">
-        <v>0.7096</v>
+        <v>0.953</v>
       </c>
       <c r="K5">
-        <v>0.0358</v>
+        <v>0.0157</v>
       </c>
       <c r="L5">
-        <v>3.7743</v>
+        <v>1.8139</v>
       </c>
       <c r="M5">
-        <v>0.0002</v>
+        <v>0.0697</v>
       </c>
       <c r="N5">
-        <v>0.0123</v>
+        <v>0.0114</v>
       </c>
       <c r="O5">
-        <v>1.9186</v>
+        <v>1.589</v>
       </c>
       <c r="P5">
-        <v>0.055</v>
+        <v>0.1121</v>
       </c>
       <c r="Q5">
-        <v>0.0245</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="R5">
-        <v>3.1511</v>
+        <v>1.3366</v>
       </c>
       <c r="S5">
-        <v>0.0016</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -749,55 +749,55 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>0.7917</v>
+        <v>0.7682</v>
       </c>
       <c r="D6">
-        <v>0.7981</v>
+        <v>0.7677</v>
       </c>
       <c r="E6">
-        <v>0.8086</v>
+        <v>0.7716</v>
       </c>
       <c r="F6">
-        <v>0.8063</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="G6">
-        <v>0.8115</v>
+        <v>0.7728</v>
       </c>
       <c r="H6">
-        <v>0.0064</v>
+        <v>-0.0005</v>
       </c>
       <c r="I6">
-        <v>0.9524</v>
+        <v>-0.2707</v>
       </c>
       <c r="J6">
-        <v>0.3409</v>
+        <v>0.7866</v>
       </c>
       <c r="K6">
-        <v>0.0105</v>
+        <v>0.0039</v>
       </c>
       <c r="L6">
-        <v>1.0044</v>
+        <v>0.5356</v>
       </c>
       <c r="M6">
-        <v>0.3152</v>
+        <v>0.5923</v>
       </c>
       <c r="N6">
-        <v>0.0146</v>
+        <v>0.0016</v>
       </c>
       <c r="O6">
-        <v>1.1997</v>
+        <v>0.2764</v>
       </c>
       <c r="P6">
-        <v>0.2303</v>
+        <v>0.7822</v>
       </c>
       <c r="Q6">
-        <v>0.0052</v>
+        <v>0.0031</v>
       </c>
       <c r="R6">
-        <v>0.5036</v>
+        <v>0.4445</v>
       </c>
       <c r="S6">
-        <v>0.6145</v>
+        <v>0.6567</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -808,55 +808,55 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>0.621</v>
+        <v>0.6156</v>
       </c>
       <c r="D7">
-        <v>0.6125</v>
+        <v>0.6141</v>
       </c>
       <c r="E7">
-        <v>0.643</v>
+        <v>0.6297</v>
       </c>
       <c r="F7">
-        <v>0.6206</v>
+        <v>0.617</v>
       </c>
       <c r="G7">
-        <v>0.6368</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="H7">
-        <v>-0.008500000000000001</v>
+        <v>-0.0015</v>
       </c>
       <c r="I7">
-        <v>-1.5301</v>
+        <v>-0.9165</v>
       </c>
       <c r="J7">
-        <v>0.126</v>
+        <v>0.3594</v>
       </c>
       <c r="K7">
-        <v>0.0305</v>
+        <v>0.0156</v>
       </c>
       <c r="L7">
-        <v>3.8819</v>
+        <v>2.6967</v>
       </c>
       <c r="M7">
-        <v>0.0001</v>
+        <v>0.007</v>
       </c>
       <c r="N7">
-        <v>-0.0005</v>
+        <v>0.0014</v>
       </c>
       <c r="O7">
-        <v>-0.053</v>
+        <v>0.2702</v>
       </c>
       <c r="P7">
-        <v>0.9577</v>
+        <v>0.787</v>
       </c>
       <c r="Q7">
-        <v>0.0163</v>
+        <v>0.0095</v>
       </c>
       <c r="R7">
-        <v>2.0922</v>
+        <v>1.7594</v>
       </c>
       <c r="S7">
-        <v>0.0364</v>
+        <v>0.0785</v>
       </c>
     </row>
   </sheetData>
